--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:13</t>
+    <t xml:space="preserve">2026-09-09 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:08</t>
+    <t xml:space="preserve">2026-09-17 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:04</t>
+    <t xml:space="preserve">2026-09-23 12:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:33</t>
+    <t xml:space="preserve">2026-10-02 13:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_biobio.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Laja</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Nacimiento</t>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Santa Juana</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Santa Bárbara</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:56</t>
+    <t xml:space="preserve">2026-10-04 08:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:58</t>
+    <t xml:space="preserve">2026-10-05 10:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -801,7 +801,7 @@
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>247802.12</v>
+        <v>247802.13</v>
       </c>
     </row>
     <row r="16">
